--- a/Pricing Logic/uploads/treasure_hunt_61.xlsx
+++ b/Pricing Logic/uploads/treasure_hunt_61.xlsx
@@ -40,7 +40,7 @@
     <t>@#</t>
   </si>
   <si>
-    <t>YES</t>
+    <t>NO</t>
   </si>
 </sst>
 </file>
